--- a/事業計画_Ver1.4.xlsx
+++ b/事業計画_Ver1.4.xlsx
@@ -13,9 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="損益計算書" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資金計画" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="原価とAX感応度" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資本政策とリターン" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業界ベンチマーク" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出所と仮置き" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資本構成の推移" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資本政策とリターン" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業界ベンチマーク" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="出所と仮置き" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +25,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot;倍&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -126,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,7 +159,7 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -195,10 +199,32 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1287,6 +1313,556 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>数字の出所と、［仮置き］の一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>投資家に聞かれて最初に困るのがここ。実測値と仮置きを混ぜないこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>出所・根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>国内 映像制作市場</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>4,580億円</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>実測</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>矢野経済研究所（BtoB映像制作）。動画コンテンツ市場6,300億とは別枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>制作費の相場帯</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>10〜500万円/本</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>実測</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>動画幹事・ムビサク（用途別の制作費相場）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>AI導入による削減率</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
+        <is>
+          <t>▲50〜90%</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>当社試算</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>工程別削減率（企画▲50・撮影▲80・機材▲80・出演▲90・編集▲50・諸経費▲30）を費用構成に当てたもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>東証グロース 上場維持基準</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>5年経過後 時価総額100億円</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>実測</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>日本取引所グループ。上場基準は改定が続くため準備期に再確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ベンチマーク各社の売上</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>「業界ベンチマーク」シート</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>実測</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>各社の有価証券報告書・決算短信。ARRは各社公表値、1ドル150円換算</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>スキルシェア市場の映像比率</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>非公表</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>確認不能</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>ココナラ決算・矢野経済のいずれも映像分野を分離開示していない</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>──────────</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr"/>
+      <c r="C10" s="16" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>AX倍率</t>
+        </is>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>1.0 → 4.0倍</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>未実証。計画の最重要前提。3倍でも営業利益率23.3%で成立することを確認済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>受注本数カーブ</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>54 → 5,594本</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>5期でSAMの1.5%。市場が制約ではなく、作る人が制約</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>1本あたり原価の内訳</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>20.5万円（AX4倍時）</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>中国クリエイター12＋ディレクション5＋ツール2＋バッファ1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ツール外販の契約数</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>法人600社／個人17,000人</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>国内の制作会社だけでは届かない。海外展開が前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>C2C の GMV</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>83億円</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ココナラの流通高に迫る規模。自動化が効いていることが前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>手数料率</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>収納代行型。資金決済法の該当性は弁護士に確認中</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>研究開発費</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>5期 16億</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>クラウドGPU・ライセンス・データ基盤</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>実効税率</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>繰越欠損金の控除後に適用。税理士に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>入金・支払サイト</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>売掛60日／買掛30日</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>契約前。ここが延びると資金繰りに直撃する</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>ツール外販の前受期間</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>180日</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>［仮置き］</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>年額一括前受の平均残高。月額課金にすると0日になり、資金計画が変わる</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>J-KISS キャップ</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>6億円（ポストマネー）</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>CAP_TABLE.md 第4章。交渉帯6〜10億。転換時のシード持分は 1.42÷6＝23.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>シリーズA の評価</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>post 15億・調達3億</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>CAP_TABLE.md 第5章。未交渉。ここが下がると創業者持分も薄まる</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>ESOP枠</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>設立時10% → 補充後9.9%</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>税制適格SOの要件は設立時に確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>IPO 公募比率</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>このままでは流通株式比率が20%で、基準25%に5ポイント不足。4期に主幹事と確定させる</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>中国の映像制作パートナー</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>社名 ［記入予定］</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>契約前。権利は日本側に帰属する設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>業務委託の契約設計</t>
+        </is>
+      </c>
+      <c r="B26" s="28" t="inlineStr">
+        <is>
+          <t>─</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>偽装請負と読まれない設計が必要。1年目に弁護士と作成する</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4924,6 +5500,1044 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>株式シェアの推移（設立 → 上場）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>出所は CAP_TABLE.md 第5章。J-KISS はポストマネー・キャップなので、転換時のシード持分は 調達額 ÷ キャップ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>資本金</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>万円</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>代表個人が全額出資</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ESOP枠（設立時）</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>後から作ると既存株主全員の希薄化になるので設立時に設計する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>J-KISS キャップ（ポストマネー）</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>億円</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>交渉帯は6〜10億。低すぎるとシリーズAで一気に薄まる</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>シード調達額</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>億円</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>目標1.5億のうち0.08億は代表個人の直接出資</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ディスカウント</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>キャップとの有利な方が適用される</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>シリーズA ポストマネー評価</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>億円</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>2028年（2期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>シリーズA 調達額</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>億円</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>これが無いと2期末に資金ショートする</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>ESOP補充後の ESOP比率</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>シリーズAで薄まった枠を戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>IPO 公募比率</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>2031年。流通株式25%を満たすには要見直し（下表）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>転換時のシード持分（シリーズA前）</t>
+        </is>
+      </c>
+      <c r="C13" s="27">
+        <f>C7/C6</f>
+        <v/>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>ポストマネー・キャップなので 1.42億 ÷ 6億</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>シリーズA の持分</t>
+        </is>
+      </c>
+      <c r="C14" s="27">
+        <f>C10/C9</f>
+        <v/>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>3億 ÷ post 15億</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>持分の推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>時期</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>イベント</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>創業者</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ESOP</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>シード</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>シリーズA</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>経営権の判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026/10</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>設立（資本金800万）</t>
+        </is>
+      </c>
+      <c r="C18" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="9">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="F18" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G18" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H18" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I18" s="29">
+        <f>SUM(D18:H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="5">
+        <f>IF(D18&gt;0.5,"経営権あり（50%超）",IF(D18&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026/10</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ESOP枠を設計</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="9">
+        <f>D18*(1-$C$5)</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>$C$5</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I19" s="29">
+        <f>SUM(D19:H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="5">
+        <f>IF(D19&gt;0.5,"経営権あり（50%超）",IF(D19&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026/10</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>J-KISS 発行（未転換）</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="inlineStr">
+        <is>
+          <t>1.42億</t>
+        </is>
+      </c>
+      <c r="D20" s="9">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="G20" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="H20" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I20" s="29">
+        <f>SUM(D20:H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="5">
+        <f>IF(D20&gt;0.5,"経営権あり（50%超）",IF(D20&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>シリーズA ＋ J-KISS転換</t>
+        </is>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>3億</t>
+        </is>
+      </c>
+      <c r="D21" s="9">
+        <f>D20*(1-$C$13)*(1-$C$14)</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>E20*(1-$C$13)*(1-$C$14)</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>$C$13*(1-$C$14)</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>$C$14</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I21" s="29">
+        <f>SUM(D21:H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="5">
+        <f>IF(D21&gt;0.5,"経営権あり（50%超）",IF(D21&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ESOP補充</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="9">
+        <f>D21*(1-$C$11)/(1-E21)</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>$C$11</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>F21*(1-$C$11)/(1-E21)</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>G21*(1-$C$11)/(1-E21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I22" s="29">
+        <f>SUM(D22:H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="5">
+        <f>IF(D22&gt;0.5,"経営権あり（50%超）",IF(D22&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>IPO 公募</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="9">
+        <f>D22*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>E22*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>F22*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>G22*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>$C$12</f>
+        <v/>
+      </c>
+      <c r="I23" s="29">
+        <f>SUM(D23:H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="5">
+        <f>IF(D23&gt;0.5,"経営権あり（50%超）",IF(D23&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>J-KISS は転換までは議決権が発生しない。1/3の線を踏まずに済むのが J-KISS を選ぶ理由のひとつ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>上場時の評価額</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>株主</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>上場時持分</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>保守 348億</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>中庸 419億</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>強気 490億</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>創業者</t>
+        </is>
+      </c>
+      <c r="B28" s="24">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="30">
+        <f>B28*348</f>
+        <v/>
+      </c>
+      <c r="E28" s="30">
+        <f>B28*419</f>
+        <v/>
+      </c>
+      <c r="F28" s="30">
+        <f>B28*490</f>
+        <v/>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>経営権は上場時に50%を割る。ただしシリーズA後も52.7%を維持できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>シード投資家</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="31">
+        <f>B29*348</f>
+        <v/>
+      </c>
+      <c r="E29" s="31">
+        <f>B29*419</f>
+        <v/>
+      </c>
+      <c r="F29" s="31">
+        <f>B29*490</f>
+        <v/>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>出資1.42億に対する取り分</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>シリーズA</t>
+        </is>
+      </c>
+      <c r="B30" s="24">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="C30" s="5" t="inlineStr"/>
+      <c r="D30" s="30">
+        <f>B30*348</f>
+        <v/>
+      </c>
+      <c r="E30" s="30">
+        <f>B30*419</f>
+        <v/>
+      </c>
+      <c r="F30" s="30">
+        <f>B30*490</f>
+        <v/>
+      </c>
+      <c r="J30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ESOP</t>
+        </is>
+      </c>
+      <c r="B31" s="24">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="C31" s="5" t="inlineStr"/>
+      <c r="D31" s="30">
+        <f>B31*348</f>
+        <v/>
+      </c>
+      <c r="E31" s="30">
+        <f>B31*419</f>
+        <v/>
+      </c>
+      <c r="F31" s="30">
+        <f>B31*490</f>
+        <v/>
+      </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>役員・従業員への配分枠</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B32" s="24">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="30">
+        <f>B32*348</f>
+        <v/>
+      </c>
+      <c r="E32" s="30">
+        <f>B32*419</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>B32*490</f>
+        <v/>
+      </c>
+      <c r="J32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>単位は億円。時価総額は「資本政策とリターン」シートのライン別評価。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>⚠ 流通株式比率 — このままでは基準25%を満たさない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>株主</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>上場時持分</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>流通株式への算入</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>創業者（役員）</t>
+        </is>
+      </c>
+      <c r="B37" s="10">
+        <f>D23</f>
+        <v/>
+      </c>
+      <c r="C37" s="5" t="inlineStr"/>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>× 除外</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>役員は除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>シード投資家</t>
+        </is>
+      </c>
+      <c r="B38" s="10">
+        <f>F23</f>
+        <v/>
+      </c>
+      <c r="C38" s="5" t="inlineStr"/>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>× 除外</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>10%超のため除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>シリーズA</t>
+        </is>
+      </c>
+      <c r="B39" s="10">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="C39" s="5" t="inlineStr"/>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>× 除外</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>10%超のため除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>ESOP</t>
+        </is>
+      </c>
+      <c r="B40" s="10">
+        <f>E23</f>
+        <v/>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>× 除外</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>役員・従業員分は除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B41" s="10">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="C41" s="5" t="inlineStr"/>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>○ 算入</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>算入</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>流通株式比率</t>
+        </is>
+      </c>
+      <c r="B42" s="33">
+        <f>H23</f>
+        <v/>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="34">
+        <f>B42-0.25</f>
+        <v/>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>基準25%に対する過不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>手当て: ①公募を25%に引き上げる（創業者42.2%→39.5%）／②公募20%＋売出し5〜8%を併用（推奨）／③上場前にVC持分を10%未満へ分散。主幹事証券が決まる4期に確定させる論点。シードのタームシートに「上場時の売出しに協力する」条項を入れておくこと。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4986,11 +6600,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>J-KISS バリュエーションキャップ</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
-        <v>6</v>
+          <t>J-KISS キャップ（ポストマネー）</t>
+        </is>
+      </c>
+      <c r="B4" s="35">
+        <f>'資本構成の推移'!C6</f>
+        <v/>
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
@@ -5004,7 +6619,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>ポストマネー・キャップ</t>
+          <t>「資本構成の推移」シートの入力を参照</t>
         </is>
       </c>
     </row>
@@ -5014,8 +6629,9 @@
           <t>シード調達額</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
-        <v>1.42</v>
+      <c r="B5" s="35">
+        <f>'資本構成の推移'!C7</f>
+        <v/>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
@@ -5040,7 +6656,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>B5/(B4+B5)</f>
+        <f>'資本構成の推移'!C13</f>
         <v/>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -5055,32 +6671,33 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>＝ 調達額 ÷（キャップ ＋ 調達額）</t>
+          <t>ポストマネー・キャップなので ＝ 調達額 ÷ キャップ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>希薄化係数 d</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="n">
-        <v>0.758</v>
+          <t>転換後の希薄化</t>
+        </is>
+      </c>
+      <c r="B7" s="36">
+        <f>B8/B6</f>
+        <v/>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>倍</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>計算</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>シリーズA3億・ESOP10%・IPO公募20%をまとめたもの</t>
+          <t>シリーズA20% → ESOP補充 → IPO公募20% の積。推移シートから逆算</t>
         </is>
       </c>
     </row>
@@ -5091,7 +6708,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>B6*B7</f>
+        <f>'資本構成の推移'!F23</f>
         <v/>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -5212,7 +6829,7 @@
         <f>E13*$B$8</f>
         <v/>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="37">
         <f>F13/$B$5</f>
         <v/>
       </c>
@@ -5249,7 +6866,7 @@
         <f>E14*$B$8</f>
         <v/>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="37">
         <f>F14/$B$5</f>
         <v/>
       </c>
@@ -5282,7 +6899,7 @@
         <f>E15*$B$8</f>
         <v/>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="37">
         <f>F15/$B$5</f>
         <v/>
       </c>
@@ -5361,7 +6978,7 @@
         <f>E19*$B$8</f>
         <v/>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="37">
         <f>F19/$B$5</f>
         <v/>
       </c>
@@ -5394,7 +7011,7 @@
         <f>E20*$B$8</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="37">
         <f>F20/$B$5</f>
         <v/>
       </c>
@@ -5416,7 +7033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5671,7 +7288,7 @@
           <t>Runway</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5698,7 +7315,7 @@
           <t>Technicolor</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>非開示</t>
         </is>
@@ -5725,7 +7342,7 @@
           <t>【当社 5期（2031年）】</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="38">
         <f>損益計算書!$G$9/100</f>
         <v/>
       </c>
@@ -5765,490 +7382,6 @@
       <c r="B17" s="10">
         <f>損益計算書!$G$7/100/210</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>数字の出所と、［仮置き］の一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>投資家に聞かれて最初に困るのがここ。実測値と仮置きを混ぜないこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>値</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>出所・根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>国内 映像制作市場</t>
-        </is>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>4,580億円</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>実測</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>矢野経済研究所（BtoB映像制作）。動画コンテンツ市場6,300億とは別枠</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>制作費の相場帯</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>10〜500万円/本</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>実測</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>動画幹事・ムビサク（用途別の制作費相場）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>AI導入による削減率</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>▲50〜90%</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>当社試算</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>工程別削減率（企画▲50・撮影▲80・機材▲80・出演▲90・編集▲50・諸経費▲30）を費用構成に当てたもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>東証グロース 上場維持基準</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>5年経過後 時価総額100億円</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>実測</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>日本取引所グループ。上場基準は改定が続くため準備期に再確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ベンチマーク各社の売上</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>「業界ベンチマーク」シート</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>実測</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>各社の有価証券報告書・決算短信。ARRは各社公表値、1ドル150円換算</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>スキルシェア市場の映像比率</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>非公表</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>確認不能</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>ココナラ決算・矢野経済のいずれも映像分野を分離開示していない</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>──────────</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="inlineStr"/>
-      <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>AX倍率</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>1.0 → 4.0倍</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>未実証。計画の最重要前提。3倍でも営業利益率23.3%で成立することを確認済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>受注本数カーブ</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>54 → 5,594本</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>5期でSAMの1.5%。市場が制約ではなく、作る人が制約</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>1本あたり原価の内訳</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>20.5万円（AX4倍時）</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>中国クリエイター12＋ディレクション5＋ツール2＋バッファ1.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>ツール外販の契約数</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>法人600社／個人17,000人</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>国内の制作会社だけでは届かない。海外展開が前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>C2C の GMV</t>
-        </is>
-      </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>83億円</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>ココナラの流通高に迫る規模。自動化が効いていることが前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>手数料率</t>
-        </is>
-      </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>収納代行型。資金決済法の該当性は弁護士に確認中</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>研究開発費</t>
-        </is>
-      </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>5期 16億</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>クラウドGPU・ライセンス・データ基盤</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>実効税率</t>
-        </is>
-      </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>繰越欠損金の控除後に適用。税理士に確認する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>入金・支払サイト</t>
-        </is>
-      </c>
-      <c r="B19" s="29" t="inlineStr">
-        <is>
-          <t>売掛60日／買掛30日</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>契約前。ここが延びると資金繰りに直撃する</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>ツール外販の前受期間</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="inlineStr">
-        <is>
-          <t>180日</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>年額一括前受の平均残高。月額課金にすると0日になり、資金計画が変わる</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>希薄化係数 d</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>0.758</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>［仮置き］</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>シリーズA3億・ESOP10%・IPO公募20%を一括で置いたもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>中国の映像制作パートナー</t>
-        </is>
-      </c>
-      <c r="B22" s="29" t="inlineStr">
-        <is>
-          <t>社名 ［記入予定］</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>契約前。権利は日本側に帰属する設計</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>業務委託の契約設計</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="inlineStr">
-        <is>
-          <t>─</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>偽装請負と読まれない設計が必要。1年目に弁護士と作成する</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/事業計画_Ver1.4.xlsx
+++ b/事業計画_Ver1.4.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%;0.0%"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0&quot;倍&quot;"/>
   </numFmts>
@@ -205,19 +205,19 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -5500,7 +5500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5795,189 +5795,151 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>2031年。流通株式25%を満たすには要見直し（下表）</t>
+          <t>2031年。新株発行なので全員が薄まる</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>IPO 売出し（シードから）</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>既存株主が売る。新株ではないので創業者は薄まらない。シードを10%未満に落とすのが目的</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>IPO 売出し（シリーズAから）</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>計画</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>シード分だけで基準を満たすため0。交渉次第で振り替えてよい</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>転換時のシード持分（シリーズA前）</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C15" s="27">
         <f>C7/C6</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>ポストマネー・キャップなので 1.42億 ÷ 6億</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>シリーズA の持分</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C16" s="27">
         <f>C10/C9</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>3億 ÷ post 15億</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>持分の推移</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>時期</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>イベント</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>創業者</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>ESOP</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>シード</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>シリーズA</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>経営権の判定</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>2026/10</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>設立（資本金800万）</t>
-        </is>
-      </c>
-      <c r="C18" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="9">
-        <f>1</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I18" s="29">
-        <f>SUM(D18:H18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="5">
-        <f>IF(D18&gt;0.5,"経営権あり（50%超）",IF(D18&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026/10</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>ESOP枠を設計</t>
-        </is>
-      </c>
-      <c r="C19" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="9">
-        <f>D18*(1-$C$5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>$C$5</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="G19" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="I19" s="29">
-        <f>SUM(D19:H19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="5">
-        <f>IF(D19&gt;0.5,"経営権あり（50%超）",IF(D19&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -5988,20 +5950,20 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>J-KISS 発行（未転換）</t>
+          <t>設立（資本金800万）</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>1.42億</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="9">
-        <f>D19</f>
+        <f>1</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>E19</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="F20" s="10">
@@ -6028,33 +5990,33 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2026/10</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>シリーズA ＋ J-KISS転換</t>
+          <t>ESOP枠を設計</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>3億</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="9">
-        <f>D20*(1-$C$13)*(1-$C$14)</f>
+        <f>D20*(1-$C$5)</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>E20*(1-$C$13)*(1-$C$14)</f>
+        <f>$C$5</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>$C$13*(1-$C$14)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="G21" s="10">
-        <f>$C$14</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="H21" s="10">
@@ -6073,33 +6035,33 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2026/10</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ESOP補充</t>
+          <t>J-KISS 発行（未転換）</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.42億</t>
         </is>
       </c>
       <c r="D22" s="9">
-        <f>D21*(1-$C$11)/(1-E21)</f>
+        <f>D21</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>$C$11</f>
+        <f>E21</f>
         <v/>
       </c>
       <c r="F22" s="10">
-        <f>F21*(1-$C$11)/(1-E21)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="G22" s="10">
-        <f>G21*(1-$C$11)/(1-E21)</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="H22" s="10">
@@ -6118,37 +6080,37 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>IPO 公募</t>
+          <t>シリーズA ＋ J-KISS転換</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3億</t>
         </is>
       </c>
       <c r="D23" s="9">
-        <f>D22*(1-$C$12)</f>
+        <f>D22*(1-$C$15)*(1-$C$16)</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>E22*(1-$C$12)</f>
+        <f>E22*(1-$C$15)*(1-$C$16)</f>
         <v/>
       </c>
       <c r="F23" s="10">
-        <f>F22*(1-$C$12)</f>
+        <f>$C$15*(1-$C$16)</f>
         <v/>
       </c>
       <c r="G23" s="10">
-        <f>G22*(1-$C$12)</f>
+        <f>$C$16</f>
         <v/>
       </c>
       <c r="H23" s="10">
-        <f>$C$12</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="I23" s="29">
@@ -6161,149 +6123,209 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>J-KISS は転換までは議決権が発生しない。1/3の線を踏まずに済むのが J-KISS を選ぶ理由のひとつ。</t>
-        </is>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ESOP補充</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" s="9">
+        <f>D23*(1-$C$11)/(1-E23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>$C$11</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>F23*(1-$C$11)/(1-E23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>G23*(1-$C$11)/(1-E23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="10">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="I24" s="29">
+        <f>SUM(D24:H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="5">
+        <f>IF(D24&gt;0.5,"経営権あり（50%超）",IF(D24&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>IPO 公募</t>
+        </is>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="9">
+        <f>D24*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="E25" s="10">
+        <f>E24*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>F24*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>G24*(1-$C$12)</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>$C$12</f>
+        <v/>
+      </c>
+      <c r="I25" s="29">
+        <f>SUM(D25:H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="5">
+        <f>IF(D25&gt;0.5,"経営権あり（50%超）",IF(D25&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>上場時の評価額</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>売出し（既存株主が売る）</t>
+        </is>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="9">
+        <f>D25</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>E25</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>F25-$C$13</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>G25-$C$14</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>H25+$C$13+$C$14</f>
+        <v/>
+      </c>
+      <c r="I26" s="29">
+        <f>SUM(D26:H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="5">
+        <f>IF(D26&gt;0.5,"経営権あり（50%超）",IF(D26&gt;0.334,"拒否権あり（1/3超）","1/3割れ"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>売出しは新株発行ではないので、創業者もESOPも薄まらない。シードの持分が動くだけで、売却代金はシードが受け取る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>上場時の評価額（売出しの代金を含む経済持分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>株主</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>上場時持分</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>経済持分</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>うち売出し</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>保守 348億</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>中庸 419億</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>強気 490億</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>創業者</t>
-        </is>
-      </c>
-      <c r="B28" s="24">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="30">
-        <f>B28*348</f>
-        <v/>
-      </c>
-      <c r="E28" s="30">
-        <f>B28*419</f>
-        <v/>
-      </c>
-      <c r="F28" s="30">
-        <f>B28*490</f>
-        <v/>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>経営権は上場時に50%を割る。ただしシリーズA後も52.7%を維持できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>シード投資家</t>
-        </is>
-      </c>
-      <c r="B29" s="24">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="31">
-        <f>B29*348</f>
-        <v/>
-      </c>
-      <c r="E29" s="31">
-        <f>B29*419</f>
-        <v/>
-      </c>
-      <c r="F29" s="31">
-        <f>B29*490</f>
-        <v/>
-      </c>
-      <c r="J29" s="7" t="inlineStr">
-        <is>
-          <t>出資1.42億に対する取り分</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>シリーズA</t>
-        </is>
-      </c>
-      <c r="B30" s="24">
-        <f>G23</f>
-        <v/>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="30">
-        <f>B30*348</f>
-        <v/>
-      </c>
-      <c r="E30" s="30">
-        <f>B30*419</f>
-        <v/>
-      </c>
-      <c r="F30" s="30">
-        <f>B30*490</f>
-        <v/>
-      </c>
-      <c r="J30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ESOP</t>
+          <t>創業者</t>
         </is>
       </c>
       <c r="B31" s="24">
-        <f>E23</f>
-        <v/>
-      </c>
-      <c r="C31" s="5" t="inlineStr"/>
+        <f>D25</f>
+        <v/>
+      </c>
+      <c r="C31" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D31" s="30">
         <f>B31*348</f>
         <v/>
@@ -6318,21 +6340,24 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>役員・従業員への配分枠</t>
+          <t>経営権は上場時に50%を割る。シリーズA後も52.7%を維持できる</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>シード投資家</t>
         </is>
       </c>
       <c r="B32" s="24">
-        <f>H23</f>
-        <v/>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
+        <f>F25</f>
+        <v/>
+      </c>
+      <c r="C32" s="10">
+        <f>$C$13</f>
+        <v/>
+      </c>
       <c r="D32" s="30">
         <f>B32*348</f>
         <v/>
@@ -6345,185 +6370,347 @@
         <f>B32*490</f>
         <v/>
       </c>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>売却代金 ＋ 保有株の合計。売出しをしても取り分は変わらない</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>単位は億円。時価総額は「資本政策とリターン」シートのライン別評価。</t>
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>シリーズA</t>
+        </is>
+      </c>
+      <c r="B33" s="24">
+        <f>G25</f>
+        <v/>
+      </c>
+      <c r="C33" s="10">
+        <f>$C$14</f>
+        <v/>
+      </c>
+      <c r="D33" s="31">
+        <f>B33*348</f>
+        <v/>
+      </c>
+      <c r="E33" s="31">
+        <f>B33*419</f>
+        <v/>
+      </c>
+      <c r="F33" s="31">
+        <f>B33*490</f>
+        <v/>
+      </c>
+      <c r="J33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ESOP</t>
+        </is>
+      </c>
+      <c r="B34" s="24">
+        <f>E25</f>
+        <v/>
+      </c>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="31">
+        <f>B34*348</f>
+        <v/>
+      </c>
+      <c r="E34" s="31">
+        <f>B34*419</f>
+        <v/>
+      </c>
+      <c r="F34" s="31">
+        <f>B34*490</f>
+        <v/>
+      </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>役員・従業員への配分枠</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>⚠ 流通株式比率 — このままでは基準25%を満たさない</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="B35" s="24">
+        <f>H25</f>
+        <v/>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="31">
+        <f>B35*348</f>
+        <v/>
+      </c>
+      <c r="E35" s="31">
+        <f>B35*419</f>
+        <v/>
+      </c>
+      <c r="F35" s="31">
+        <f>B35*490</f>
+        <v/>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>新株発行分</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>単位は億円。売出しは新株発行ではないので、売った側の経済持分は減らない（代金で受け取る）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>流通株式比率 — 基準25%を満たす設計</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>株主</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>上場時持分</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>上場後の保有持分</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>10%の判定</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>流通株式への算入</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>算入される持分</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>理由</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>創業者（役員）</t>
-        </is>
-      </c>
-      <c r="B37" s="10">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="C37" s="5" t="inlineStr"/>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>× 除外</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>役員は除外</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>シード投資家</t>
-        </is>
-      </c>
-      <c r="B38" s="10">
-        <f>F23</f>
-        <v/>
-      </c>
-      <c r="C38" s="5" t="inlineStr"/>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>× 除外</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr">
-        <is>
-          <t>10%超のため除外</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>シリーズA</t>
-        </is>
-      </c>
-      <c r="B39" s="10">
-        <f>G23</f>
-        <v/>
-      </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>× 除外</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr">
-        <is>
-          <t>10%超のため除外</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>ESOP</t>
-        </is>
-      </c>
-      <c r="B40" s="10">
-        <f>E23</f>
-        <v/>
-      </c>
-      <c r="C40" s="5" t="inlineStr"/>
+          <t>創業者（役員）</t>
+        </is>
+      </c>
+      <c r="B40" s="24">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D40" s="17" t="inlineStr">
         <is>
           <t>× 除外</t>
         </is>
       </c>
+      <c r="E40" s="24" t="n">
+        <v>0</v>
+      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>役員・従業員分は除外</t>
+          <t>役員の保有分は除外される</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>公募</t>
-        </is>
-      </c>
-      <c r="B41" s="10">
-        <f>H23</f>
-        <v/>
-      </c>
-      <c r="C41" s="5" t="inlineStr"/>
-      <c r="D41" s="16" t="inlineStr">
+          <t>ESOP枠</t>
+        </is>
+      </c>
+      <c r="B41" s="24">
+        <f>E26</f>
+        <v/>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>× 除外</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>役員・従業員分は除外される</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>シード投資家 保有分</t>
+        </is>
+      </c>
+      <c r="B42" s="24">
+        <f>F26</f>
+        <v/>
+      </c>
+      <c r="C42" s="16">
+        <f>IF(B42&lt;0.1,"10%未満","10%以上")</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>IF(B42&lt;0.1,"○ 算入","× 除外")</f>
+        <v/>
+      </c>
+      <c r="E42" s="24">
+        <f>IF(B42&lt;0.1,B42,0)</f>
+        <v/>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>10%未満なら全株が算入される。売出しでここを越える</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>シリーズA 保有分</t>
+        </is>
+      </c>
+      <c r="B43" s="24">
+        <f>G26</f>
+        <v/>
+      </c>
+      <c r="C43" s="16">
+        <f>IF(B43&lt;0.1,"10%未満","10%以上")</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>IF(B43&lt;0.1,"○ 算入","× 除外")</f>
+        <v/>
+      </c>
+      <c r="E43" s="24">
+        <f>IF(B43&lt;0.1,B43,0)</f>
+        <v/>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>10%以上なので除外。シードだけで基準を満たすため売出しは0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>公募・売出し</t>
+        </is>
+      </c>
+      <c r="B44" s="24">
+        <f>H26</f>
+        <v/>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>○ 算入</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>算入</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="E44" s="24">
+        <f>B44</f>
+        <v/>
+      </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>市場に出た分。全額が算入される</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>流通株式比率</t>
         </is>
       </c>
-      <c r="B42" s="33">
-        <f>H23</f>
-        <v/>
-      </c>
-      <c r="C42" s="5" t="inlineStr"/>
-      <c r="D42" s="34">
-        <f>B42-0.25</f>
-        <v/>
-      </c>
-      <c r="J42" s="7" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr"/>
+      <c r="C45" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="9">
+        <f>SUM(E40:E44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>基準25%に対する過不足</t>
         </is>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>手当て: ①公募を25%に引き上げる（創業者42.2%→39.5%）／②公募20%＋売出し5〜8%を併用（推奨）／③上場前にVC持分を10%未満へ分散。主幹事証券が決まる4期に確定させる論点。シードのタームシートに「上場時の売出しに協力する」条項を入れておくこと。</t>
+      <c r="B46" s="5" t="inlineStr"/>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="32">
+        <f>IF(E45&gt;=0.25,"○ 満たす","× 不足")</f>
+        <v/>
+      </c>
+      <c r="E46" s="33">
+        <f>E45-0.25</f>
+        <v/>
+      </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>東証グロースの上場維持基準</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>仕組み: シードが5.5%を売出すと保有が10%未満になり、残りの保有株も一括で流通株式に算入される。公募20%だけなら20%、売出しを足すと34.5%まで跳ね上がるのはこのため。公募を25%に上げる案より、創業者持分が2.6ポイント厚く残る（42.2% vs 39.5%）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>⚠ 残る論点: 時価総額348億で25.5%を売り出すと、公開規模は約89億になる。グロース市場としては大きく、機関投資家の需要が要る。主幹事が決まる4期に規模を再設計すること。シードのタームシートには「上場時の売出しに協力する」条項を入れておく。</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6843,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>'資本構成の推移'!C13</f>
+        <f>'資本構成の推移'!C15</f>
         <v/>
       </c>
       <c r="C6" s="16" t="inlineStr">
@@ -6708,7 +6895,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>'資本構成の推移'!F23</f>
+        <f>'資本構成の推移'!F25</f>
         <v/>
       </c>
       <c r="C8" s="16" t="inlineStr">
